--- a/public/daily_template.xlsx
+++ b/public/daily_template.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
   <si>
     <t xml:space="preserve">매출 일마감</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t xml:space="preserve">문희선</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예윤진</t>
   </si>
   <si>
     <t xml:space="preserve">원    장</t>
@@ -600,9 +603,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>319320</xdr:colOff>
+      <xdr:colOff>318960</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>227880</xdr:rowOff>
+      <xdr:rowOff>227520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -616,7 +619,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5387400" y="137160"/>
-          <a:ext cx="675360" cy="90720"/>
+          <a:ext cx="675000" cy="90360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -934,8 +937,12 @@
       <c r="J11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
+      <c r="A12" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>17</v>
+      </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
       <c r="E12" s="14"/>
@@ -950,10 +957,10 @@
     </row>
     <row r="13" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -969,10 +976,10 @@
     </row>
     <row r="14" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
@@ -1045,7 +1052,7 @@
     </row>
     <row r="18" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="14"/>
@@ -1182,7 +1189,7 @@
     </row>
     <row r="27" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>1</v>
@@ -1210,11 +1217,11 @@
     </row>
     <row r="28" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="17" t="s">
@@ -1224,7 +1231,7 @@
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="21" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J28" s="21"/>
     </row>
@@ -1348,7 +1355,7 @@
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F34" s="20" t="n">
         <f aca="false">IF(OR(G27="",F35=""),"",G27-F35)</f>

--- a/public/daily_template.xlsx
+++ b/public/daily_template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="27">
   <si>
     <t xml:space="preserve">매출 일마감</t>
   </si>
@@ -73,9 +73,6 @@
   </si>
   <si>
     <t xml:space="preserve">이수민</t>
-  </si>
-  <si>
-    <t xml:space="preserve">나시은</t>
   </si>
   <si>
     <t xml:space="preserve">문희선</t>
@@ -603,9 +600,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>318960</xdr:colOff>
+      <xdr:colOff>318600</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>227520</xdr:rowOff>
+      <xdr:rowOff>227160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -619,7 +616,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="5387400" y="137160"/>
-          <a:ext cx="675000" cy="90360"/>
+          <a:ext cx="674640" cy="90000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -938,10 +935,10 @@
     </row>
     <row r="12" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" s="14"/>
       <c r="D12" s="14"/>
@@ -957,10 +954,10 @@
     </row>
     <row r="13" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" s="14"/>
       <c r="D13" s="14"/>
@@ -975,12 +972,8 @@
       <c r="J13" s="14"/>
     </row>
     <row r="14" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>21</v>
-      </c>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="14"/>
       <c r="D14" s="14"/>
       <c r="E14" s="14"/>
@@ -1052,7 +1045,7 @@
     </row>
     <row r="18" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="17"/>
       <c r="C18" s="14"/>
@@ -1189,7 +1182,7 @@
     </row>
     <row r="27" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B27" s="17" t="s">
         <v>1</v>
@@ -1217,11 +1210,11 @@
     </row>
     <row r="28" customFormat="false" ht="20" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="20" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D28" s="20"/>
       <c r="E28" s="17" t="s">
@@ -1231,7 +1224,7 @@
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
       <c r="I28" s="21" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J28" s="21"/>
     </row>
@@ -1355,7 +1348,7 @@
       </c>
       <c r="D34" s="23"/>
       <c r="E34" s="24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F34" s="20" t="n">
         <f aca="false">IF(OR(G27="",F35=""),"",G27-F35)</f>
